--- a/data/cutting_conditions/CFRP.xlsx
+++ b/data/cutting_conditions/CFRP.xlsx
@@ -1,18 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D612200A-E785-45EB-B467-EC0EC94E536D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -44,18 +56,17 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Cast_iron_FC250</t>
+    <t>RPM(rev/min)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RPM(rev/min)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>CFRP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -388,7 +399,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J92"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -421,7 +432,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -429,7 +440,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -456,7 +467,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -471,7 +482,7 @@
         <v>0.06</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F66" si="0">ROUND(1000*D3/(PI()*B3),0)</f>
+        <f t="shared" ref="F3:F50" si="0">ROUND(1000*D3/(PI()*B3),0)</f>
         <v>4775</v>
       </c>
       <c r="G3">
@@ -483,7 +494,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -510,7 +521,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -537,7 +548,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -564,7 +575,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -591,7 +602,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -618,7 +629,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>4.5</v>
@@ -646,7 +657,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>4.5</v>
@@ -674,7 +685,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>4.5</v>
@@ -702,7 +713,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>4.5</v>
@@ -730,7 +741,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>4.5</v>
@@ -758,7 +769,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>4.5</v>
@@ -786,7 +797,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>4.5</v>
@@ -814,7 +825,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B16">
         <v>4.8</v>
@@ -842,7 +853,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B17">
         <v>4.8</v>
@@ -870,7 +881,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>4.8</v>
@@ -898,7 +909,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>4.8</v>
@@ -926,7 +937,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20">
         <v>4.8</v>
@@ -954,7 +965,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B21">
         <v>4.8</v>
@@ -982,7 +993,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B22">
         <v>4.8</v>
@@ -1010,7 +1021,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -1038,7 +1049,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -1066,7 +1077,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -1094,7 +1105,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26">
         <v>5</v>
@@ -1122,7 +1133,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B27">
         <v>5</v>
@@ -1150,7 +1161,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -1178,7 +1189,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -1206,7 +1217,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30">
         <v>5.5</v>
@@ -1234,7 +1245,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31">
         <v>5.5</v>
@@ -1262,7 +1273,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32">
         <v>5.5</v>
@@ -1290,7 +1301,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33">
         <v>5.5</v>
@@ -1318,7 +1329,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B34">
         <v>5.5</v>
@@ -1346,7 +1357,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B35">
         <v>5.5</v>
@@ -1374,7 +1385,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B36">
         <v>5.5</v>
@@ -1402,7 +1413,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B37">
         <v>6</v>
@@ -1430,7 +1441,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1458,7 +1469,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B39">
         <v>6</v>
@@ -1486,7 +1497,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40">
         <v>6</v>
@@ -1514,7 +1525,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41">
         <v>6</v>
@@ -1542,7 +1553,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B42">
         <v>6</v>
@@ -1570,7 +1581,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B43">
         <v>6</v>
@@ -1598,7 +1609,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B44">
         <v>6.5</v>
@@ -1626,7 +1637,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B45">
         <v>6.5</v>
@@ -1654,7 +1665,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B46">
         <v>6.5</v>
@@ -1682,7 +1693,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B47">
         <v>6.5</v>
@@ -1710,7 +1721,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B48">
         <v>6.5</v>
@@ -1738,7 +1749,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B49">
         <v>6.5</v>
@@ -1766,7 +1777,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B50">
         <v>6.5</v>
